--- a/claude-finance-analyzer/importer/finance.xlsx
+++ b/claude-finance-analyzer/importer/finance.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>Aktie</t>
   </si>
@@ -19,7 +19,58 @@
     <t>Menge</t>
   </si>
   <si>
-    <t>xtracker AI</t>
+    <t>Emittent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy in </t>
+  </si>
+  <si>
+    <t>Anzahl</t>
+  </si>
+  <si>
+    <t>AI &amp; Big Data USD ( Acc)</t>
+  </si>
+  <si>
+    <t>Xtrackers</t>
+  </si>
+  <si>
+    <t>Core MSCI World USD (Acc)</t>
+  </si>
+  <si>
+    <t>ishares</t>
+  </si>
+  <si>
+    <t>S&amp;P 500 Information Tech USD (Acc)</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crowdstrike Holdings </t>
+  </si>
+  <si>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>Physical Swiss Gold USD</t>
+  </si>
+  <si>
+    <t>WisdomTree</t>
+  </si>
+  <si>
+    <t>Bitcoin</t>
+  </si>
+  <si>
+    <t>Physcical Gold USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple </t>
+  </si>
+  <si>
+    <t>Meta</t>
+  </si>
+  <si>
+    <t>Netflix</t>
   </si>
 </sst>
 </file>
@@ -56,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -64,6 +115,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -282,6 +336,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="28.88"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -290,13 +347,197 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>140.0</v>
+        <v>1687.96</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1">
+        <v>164.3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>8.89</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1204.5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1">
+        <v>110.97</v>
+      </c>
+      <c r="E3" s="1">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1">
+        <v>820.51</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1">
+        <v>34.69</v>
+      </c>
+      <c r="E4" s="1">
+        <v>19.51</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1">
+        <v>562.55</v>
+      </c>
+      <c r="D5" s="1">
+        <v>124.16</v>
+      </c>
+      <c r="E5" s="1">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1">
+        <v>226.92</v>
+      </c>
+      <c r="D6" s="1">
+        <v>226.92</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1">
+        <v>201.53</v>
+      </c>
+      <c r="D7" s="1">
+        <v>352.54</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1">
+        <v>121.38</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1">
+        <v>218.48</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1">
+        <v>87.25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>90794.49</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.0012</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1">
+        <v>43.02</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1">
+        <v>43.92</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.569</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>207.95</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27.83</v>
+      </c>
+      <c r="D12" s="1">
+        <v>472.2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1">
+        <v>29.46</v>
+      </c>
+      <c r="D13" s="1">
+        <v>63.39</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>

--- a/claude-finance-analyzer/importer/finance.xlsx
+++ b/claude-finance-analyzer/importer/finance.xlsx
@@ -11,11 +11,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Aktie</t>
   </si>
   <si>
+    <t>Ticker</t>
+  </si>
+  <si>
     <t>Menge</t>
   </si>
   <si>
@@ -31,46 +34,82 @@
     <t>AI &amp; Big Data USD ( Acc)</t>
   </si>
   <si>
+    <t>XAIX</t>
+  </si>
+  <si>
     <t>Xtrackers</t>
   </si>
   <si>
     <t>Core MSCI World USD (Acc)</t>
   </si>
   <si>
+    <t>EUNL</t>
+  </si>
+  <si>
     <t>ishares</t>
   </si>
   <si>
     <t>S&amp;P 500 Information Tech USD (Acc)</t>
   </si>
   <si>
+    <t>QDVE</t>
+  </si>
+  <si>
     <t>NVIDIA</t>
   </si>
   <si>
+    <t>NVDA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Crowdstrike Holdings </t>
   </si>
   <si>
+    <t>CRWD</t>
+  </si>
+  <si>
     <t>Tesla</t>
   </si>
   <si>
+    <t>TSLA</t>
+  </si>
+  <si>
     <t>Physical Swiss Gold USD</t>
   </si>
   <si>
+    <t>SGLD</t>
+  </si>
+  <si>
     <t>WisdomTree</t>
   </si>
   <si>
     <t>Bitcoin</t>
   </si>
   <si>
+    <t>BTC</t>
+  </si>
+  <si>
     <t>Physcical Gold USD</t>
   </si>
   <si>
+    <t>PHAU</t>
+  </si>
+  <si>
     <t xml:space="preserve">Apple </t>
   </si>
   <si>
+    <t>AAPL</t>
+  </si>
+  <si>
     <t>Meta</t>
   </si>
   <si>
+    <t>META</t>
+  </si>
+  <si>
     <t>Netflix</t>
+  </si>
+  <si>
+    <t>NFLX</t>
   </si>
 </sst>
 </file>
@@ -356,187 +395,226 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2">
         <v>1687.96</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1">
         <v>164.3</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>8.89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
         <v>1204.5</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1">
         <v>110.97</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>10.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1">
         <v>820.51</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1">
         <v>34.69</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>19.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
         <v>562.55</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>124.16</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>11.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1">
         <v>226.92</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>226.92</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>5.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1">
         <v>201.53</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>352.54</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>0.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1">
         <v>121.38</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="D8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="1">
         <v>218.48</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>0.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1">
         <v>87.25</v>
       </c>
-      <c r="D9" s="3">
+      <c r="E9" s="3">
         <v>90794.49</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>0.0012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1">
         <v>43.02</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1">
         <v>43.92</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>0.569</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1">
         <v>31.0</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>207.95</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>0.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1">
         <v>27.83</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>472.2</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>0.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1">
         <v>29.46</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>63.39</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>0.39</v>
       </c>
     </row>

--- a/claude-finance-analyzer/importer/finance.xlsx
+++ b/claude-finance-analyzer/importer/finance.xlsx
@@ -25,7 +25,7 @@
     <t>Emittent</t>
   </si>
   <si>
-    <t xml:space="preserve">Buy in </t>
+    <t xml:space="preserve">Buyin </t>
   </si>
   <si>
     <t>Anzahl</t>
@@ -34,7 +34,7 @@
     <t>AI &amp; Big Data USD ( Acc)</t>
   </si>
   <si>
-    <t>XAIX</t>
+    <t>XAIX.DE</t>
   </si>
   <si>
     <t>Xtrackers</t>
@@ -43,7 +43,7 @@
     <t>Core MSCI World USD (Acc)</t>
   </si>
   <si>
-    <t>EUNL</t>
+    <t>EUNL.DE</t>
   </si>
   <si>
     <t>ishares</t>
@@ -52,7 +52,7 @@
     <t>S&amp;P 500 Information Tech USD (Acc)</t>
   </si>
   <si>
-    <t>QDVE</t>
+    <t>QDVE.DE</t>
   </si>
   <si>
     <t>NVIDIA</t>
@@ -76,7 +76,7 @@
     <t>Physical Swiss Gold USD</t>
   </si>
   <si>
-    <t>SGLD</t>
+    <t>SGLD.DE</t>
   </si>
   <si>
     <t>WisdomTree</t>
@@ -119,7 +119,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;€&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -130,6 +130,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="2">
@@ -146,14 +154,20 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -406,7 +420,7 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>1687.96</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -423,7 +437,7 @@
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="1">
@@ -443,7 +457,7 @@
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="1">
@@ -514,7 +528,7 @@
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="1">
@@ -540,7 +554,7 @@
       <c r="C9" s="1">
         <v>87.25</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="5">
         <v>90794.49</v>
       </c>
       <c r="F9" s="1">
@@ -619,6 +633,12 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="B2"/>
+    <hyperlink r:id="rId2" ref="B3"/>
+    <hyperlink r:id="rId3" ref="B4"/>
+    <hyperlink r:id="rId4" ref="B8"/>
+  </hyperlinks>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>